--- a/data/parallelcomputing.xlsx
+++ b/data/parallelcomputing.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R入門\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A6359D-4984-47AA-A9B9-B903942E4390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{079C8242-09B7-41B4-A728-30ACBAD2F1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{C45E6CDC-B319-4B1F-BE46-BDD518BB0C90}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" activeTab="1" xr2:uid="{C45E6CDC-B319-4B1F-BE46-BDD518BB0C90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -757,6 +752,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -836,5 +832,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>